--- a/consent_forms/029_international_non_disclosure_agreement_nda_form--consent_forms.xlsx
+++ b/consent_forms/029_international_non_disclosure_agreement_nda_form--consent_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -888,12 +888,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_signed_on</t>
+          <t>non_disclosure_agreement_signed_on_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Non Disclosure Agreement Signed On</t>
+          <t>Non Disclosure Agreement Signed On 2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
@@ -916,7 +916,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Non Disclosure Agreement Term</t>
+          <t>Non Disclosure Agreement Agreement Term</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
@@ -1008,7 +1008,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Non Disclosure Agreement Term In Years</t>
+          <t>Non Disclosure Agreement Agreement Term Years Years</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term</t>
+          <t>non_disclosure_agreement_agreement_term_2</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Non Disclosure Agreement Term</t>
+          <t>Non Disclosure Agreement Agreement Term 2</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1098,12 +1098,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C56"/>
+  <dimension ref="A1:C36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1403,80 +1403,80 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>eastern</t>
+          <t>utc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Eastern</t>
+          <t>UTC</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_signed_by_time_zone_choices</t>
+          <t>non_disclosure_agreement_agreement_term_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>central</t>
+          <t>30_days</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Central</t>
+          <t>30 days</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_signed_by_time_zone_choices</t>
+          <t>non_disclosure_agreement_agreement_term_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>mountain</t>
+          <t>90_days</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Mountain</t>
+          <t>90 days</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_signed_by_time_zone_choices</t>
+          <t>non_disclosure_agreement_agreement_term_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>pacific</t>
+          <t>180_days</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pacific</t>
+          <t>180 days</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_signed_by_time_zone_choices</t>
+          <t>non_disclosure_agreement_agreement_term_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>utc</t>
+          <t>1_month</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>UTC</t>
+          <t>1 month</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>30_days</t>
+          <t>6_months</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>30 days</t>
+          <t>6 months</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>90_days</t>
+          <t>1_year</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>90 days</t>
+          <t>1 year</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>180_days</t>
+          <t>2_years</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>180 days</t>
+          <t>2 years</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1_month</t>
+          <t>3_years</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1 month</t>
+          <t>3 years</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>6_months</t>
+          <t>4_years</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>6 months</t>
+          <t>4 years</t>
         </is>
       </c>
     </row>
@@ -1573,488 +1573,148 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>1_year</t>
+          <t>5_years</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1 year</t>
+          <t>5 years</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_choices</t>
+          <t>non_disclosure_agreement_agreement_term_days_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2_years</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>2 years</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_choices</t>
+          <t>non_disclosure_agreement_agreement_term_days_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>3_years</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3 years</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_choices</t>
+          <t>non_disclosure_agreement_agreement_term_months_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>4_years</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4 years</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_choices</t>
+          <t>non_disclosure_agreement_agreement_term_months_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>5_years</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>5 years</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_days_choices</t>
+          <t>non_disclosure_agreement_agreement_term_years_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_days_choices</t>
+          <t>non_disclosure_agreement_agreement_term_years_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>90</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_days_choices</t>
+          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>i_agree</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>180</t>
+          <t>I agree</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>non_disclosure_agreement_agreement_term_days_choices</t>
+          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>i_do_not_agree</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_days_choices</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_months_choices</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_months_choices</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_months_choices</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_months_choices</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_choices</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_choices</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_choices</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_choices</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>non_disclosure_agreement_agreement_term_years_years_choices</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>10</t>
+          <t>I do not agree</t>
         </is>
       </c>
     </row>
